--- a/artfynd/A 62266-2021 artfynd.xlsx
+++ b/artfynd/A 62266-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62266-2021 artfynd.xlsx
+++ b/artfynd/A 62266-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103897171</v>
+        <v>103912060</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735551.2342325177</v>
+        <v>735335</v>
       </c>
       <c r="R2" t="n">
-        <v>7089380.786227854</v>
+        <v>7089431</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103895644</v>
+        <v>103895727</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,40 +794,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vännäs, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735331.1095618424</v>
+        <v>735379</v>
       </c>
       <c r="R3" t="n">
-        <v>7089242.926939736</v>
+        <v>7089232</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -906,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103896504</v>
+        <v>103896450</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735369.6554238563</v>
+        <v>735375</v>
       </c>
       <c r="R4" t="n">
-        <v>7089337.462344713</v>
+        <v>7089314</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1019,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103895727</v>
+        <v>103910881</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735379.2994297276</v>
+        <v>735601</v>
       </c>
       <c r="R5" t="n">
-        <v>7089232.828058813</v>
+        <v>7089127</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,22 +1065,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103895734</v>
+        <v>103896941</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,35 +1118,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vännäs, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735379.2994297276</v>
+        <v>735482</v>
       </c>
       <c r="R6" t="n">
-        <v>7089232.828058813</v>
+        <v>7089371</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1180,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1190,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,6 +1199,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1245,60 +1218,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103896190</v>
+        <v>103895715</v>
       </c>
       <c r="B7" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100077</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vännäs, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735359.9712980592</v>
+        <v>735379</v>
       </c>
       <c r="R7" t="n">
-        <v>7089230.488803069</v>
+        <v>7089232</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,37 +1326,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103895652</v>
+        <v>103896613</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735331.1095618424</v>
+        <v>735357</v>
       </c>
       <c r="R8" t="n">
-        <v>7089242.926939736</v>
+        <v>7089333</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1443,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,12 +1437,7 @@
         <v>103896643</v>
       </c>
       <c r="B9" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735365.6304273081</v>
+        <v>735365</v>
       </c>
       <c r="R9" t="n">
-        <v>7089361.506909812</v>
+        <v>7089361</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1593,51 +1542,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103896537</v>
+        <v>103911305</v>
       </c>
       <c r="B10" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>5321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vännäs, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735352.7532064922</v>
+        <v>735626</v>
       </c>
       <c r="R10" t="n">
-        <v>7089326.451966864</v>
+        <v>7089193</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1664,22 +1610,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,6 +1634,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1706,58 +1653,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103896773</v>
+        <v>103895652</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vännäs, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735417.5868368482</v>
+        <v>735331</v>
       </c>
       <c r="R11" t="n">
-        <v>7089354.348682873</v>
+        <v>7089243</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1789,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,37 +1761,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103896450</v>
+        <v>103895734</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735375.00277308</v>
+        <v>735379</v>
       </c>
       <c r="R12" t="n">
-        <v>7089313.51706536</v>
+        <v>7089232</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1902,7 +1832,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1842,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,37 +1869,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103896709</v>
+        <v>103896504</v>
       </c>
       <c r="B13" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1980,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735382.1224633423</v>
+        <v>735370</v>
       </c>
       <c r="R13" t="n">
-        <v>7089389.750734242</v>
+        <v>7089338</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2052,37 +1977,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103895715</v>
+        <v>103910864</v>
       </c>
       <c r="B14" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2093,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735379.2994297276</v>
+        <v>735636</v>
       </c>
       <c r="R14" t="n">
-        <v>7089232.828058813</v>
+        <v>7089109</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2123,22 +2043,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,37 +2085,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103896749</v>
+        <v>103896537</v>
       </c>
       <c r="B15" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2206,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735396.3410792033</v>
+        <v>735353</v>
       </c>
       <c r="R15" t="n">
-        <v>7089359.833100719</v>
+        <v>7089326</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2278,15 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103896613</v>
+        <v>103896749</v>
       </c>
       <c r="B16" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2319,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735356.7304410903</v>
+        <v>735396</v>
       </c>
       <c r="R16" t="n">
-        <v>7089332.505985236</v>
+        <v>7089360</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2391,37 +2301,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103897094</v>
+        <v>103910880</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2432,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735525.2093455121</v>
+        <v>735602</v>
       </c>
       <c r="R17" t="n">
-        <v>7089367.317453704</v>
+        <v>7089127</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2462,22 +2367,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,15 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103912060</v>
+        <v>103897094</v>
       </c>
       <c r="B18" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2545,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735334.7026768888</v>
+        <v>735526</v>
       </c>
       <c r="R18" t="n">
-        <v>7089430.893415679</v>
+        <v>7089367</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2575,22 +2475,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,15 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103911789</v>
+        <v>103897171</v>
       </c>
       <c r="B19" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735496.6751094062</v>
+        <v>735551</v>
       </c>
       <c r="R19" t="n">
-        <v>7089334.181969451</v>
+        <v>7089381</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2688,22 +2583,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,53 +2625,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103896941</v>
+        <v>103911789</v>
       </c>
       <c r="B20" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vännäs, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>735482.3661114039</v>
+        <v>735497</v>
       </c>
       <c r="R20" t="n">
-        <v>7089371.175637259</v>
+        <v>7089334</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2803,22 +2691,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,7 +2715,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2843,6 +2730,459 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>103896709</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vännäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>735382</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7089390</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>103896190</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vännäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>735360</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7089230</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>103895644</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vännäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>735331</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7089243</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>103896773</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vännäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>735417</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7089354</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-10-03</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62266-2021 artfynd.xlsx
+++ b/artfynd/A 62266-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103912060</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103895727</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896450</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103910881</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896941</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103895715</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896613</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896643</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103911305</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103895652</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1866,6 +1921,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103895734</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1974,6 +2034,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896504</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2082,6 +2147,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103910864</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896537</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2298,6 +2373,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896749</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2406,6 +2486,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103910880</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2514,6 +2599,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103897094</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2622,6 +2712,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103897171</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2730,6 +2825,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103911789</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2838,6 +2938,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896709</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2955,6 +3060,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896190</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3068,6 +3178,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103895644</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3183,8 +3298,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103896773</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>